--- a/reports/滨江一号_2026-06-20_to_2026-06-21_多日复查.xlsx
+++ b/reports/滨江一号_2026-06-20_to_2026-06-21_多日复查.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-21 05:28:07</t>
+          <t>2026-06-21 05:41:57</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
